--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.47619036464368</v>
+        <v>7.552380934254599</v>
       </c>
       <c r="D2" t="n">
-        <v>46.82219613455214</v>
+        <v>7.608606871864724</v>
       </c>
       <c r="E2" t="n">
-        <v>14.47016116150828</v>
+        <v>2.351401188745095</v>
       </c>
       <c r="F2" t="n">
-        <v>13.69564432265938</v>
+        <v>2.225542202432149</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.9940910796927</v>
+        <v>2.111539800450065</v>
       </c>
       <c r="D3" t="n">
-        <v>13.65457911706536</v>
+        <v>2.218869106523122</v>
       </c>
       <c r="E3" t="n">
-        <v>14.47016116150828</v>
+        <v>2.351401188745095</v>
       </c>
       <c r="F3" t="n">
-        <v>13.69564432265938</v>
+        <v>2.225542202432149</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.75251662913601</v>
+        <v>5.484783952234602</v>
       </c>
       <c r="D4" t="n">
-        <v>34.31784781963817</v>
+        <v>5.576650270691204</v>
       </c>
       <c r="E4" t="n">
-        <v>14.47016116150828</v>
+        <v>2.351401188745095</v>
       </c>
       <c r="F4" t="n">
-        <v>13.69564432265938</v>
+        <v>2.225542202432149</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.40815648157579</v>
+        <v>9.003825428256066</v>
       </c>
       <c r="D5" t="n">
-        <v>55.06418157364368</v>
+        <v>8.947929505717099</v>
       </c>
       <c r="E5" t="n">
-        <v>14.47016116150828</v>
+        <v>2.351401188745095</v>
       </c>
       <c r="F5" t="n">
-        <v>13.69564432265938</v>
+        <v>2.225542202432149</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.86890865008069</v>
+        <v>2.416197655638113</v>
       </c>
       <c r="D6" t="n">
-        <v>17.36784313922261</v>
+        <v>2.822274510123675</v>
       </c>
       <c r="E6" t="n">
-        <v>14.47016116150828</v>
+        <v>2.351401188745095</v>
       </c>
       <c r="F6" t="n">
-        <v>13.69564432265938</v>
+        <v>2.225542202432149</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.2020330169178</v>
+        <v>7.832830365249143</v>
       </c>
       <c r="D7" t="n">
-        <v>47.28980771720823</v>
+        <v>7.684593754046337</v>
       </c>
       <c r="E7" t="n">
-        <v>14.47016116150828</v>
+        <v>2.351401188745095</v>
       </c>
       <c r="F7" t="n">
-        <v>13.69564432265938</v>
+        <v>2.225542202432149</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.55674558049964</v>
+        <v>5.940471156831192</v>
       </c>
       <c r="D8" t="n">
-        <v>35.52340129743877</v>
+        <v>5.772552710833801</v>
       </c>
       <c r="E8" t="n">
-        <v>14.47016116150828</v>
+        <v>2.351401188745095</v>
       </c>
       <c r="F8" t="n">
-        <v>13.69564432265938</v>
+        <v>2.225542202432149</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.78839518241899</v>
+        <v>7.115614217143087</v>
       </c>
       <c r="D9" t="n">
-        <v>42.77565000450058</v>
+        <v>6.951043125731345</v>
       </c>
       <c r="E9" t="n">
-        <v>14.47016116150828</v>
+        <v>2.351401188745095</v>
       </c>
       <c r="F9" t="n">
-        <v>13.69564432265938</v>
+        <v>2.225542202432149</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
